--- a/server/templates/employee-template.xlsx
+++ b/server/templates/employee-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\projects\nanafruit-hrm\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79763476-1D03-48BF-AC33-B90EA5588C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD648A8D-A959-4F0A-9C0D-98303BA531A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>รหัสลายนิ้วมือ</t>
   </si>
@@ -282,13 +282,16 @@
   </si>
   <si>
     <t>ประจำ (รายเดือน)</t>
+  </si>
+  <si>
+    <t>EMP-IMP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,16 +319,35 @@
       <name val="TH Sarabun New"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="TH Sarabun New"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -348,61 +370,15 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -412,7 +388,10 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -729,131 +708,136 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:Q3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" style="4" customWidth="1"/>
-    <col min="11" max="12" width="17.28515625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="21.140625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.85546875" style="4" customWidth="1"/>
-    <col min="16" max="16" width="19.85546875" style="4" customWidth="1"/>
-    <col min="17" max="17" width="20.140625" style="4" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="15.5703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.28515625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.28515625" style="3" customWidth="1"/>
+    <col min="11" max="12" width="17.28515625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="21.140625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="17.85546875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="19.85546875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="20.140625" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="6">
         <v>46235</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="6">
         <v>46235</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="4" t="s">
         <v>26</v>
       </c>
     </row>

--- a/server/templates/employee-template.xlsx
+++ b/server/templates/employee-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\projects\nanafruit-hrm\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD648A8D-A959-4F0A-9C0D-98303BA531A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E163F3F6-F101-4FC1-8E59-E57E7918C525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>รหัสลายนิ้วมือ</t>
   </si>
@@ -285,6 +285,18 @@
   </si>
   <si>
     <t>EMP-IMP</t>
+  </si>
+  <si>
+    <t>หัวหน้างาน</t>
+  </si>
+  <si>
+    <t>EMPCODE001</t>
+  </si>
+  <si>
+    <t>กลุ่ม OT</t>
+  </si>
+  <si>
+    <t>OT Normal</t>
   </si>
 </sst>
 </file>
@@ -708,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="3" customWidth="1"/>
@@ -721,21 +733,22 @@
     <col min="8" max="8" width="11.42578125" style="3" customWidth="1"/>
     <col min="9" max="9" width="19.7109375" style="3" customWidth="1"/>
     <col min="10" max="10" width="20.28515625" style="3" customWidth="1"/>
-    <col min="11" max="12" width="17.28515625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="21.140625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="17.85546875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="19.85546875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="20.140625" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="3"/>
+    <col min="11" max="13" width="17.28515625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="21.140625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="16.5703125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="17.85546875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="19.85546875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="20.140625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="19.85546875" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
@@ -773,22 +786,28 @@
         <v>28</v>
       </c>
       <c r="M2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="O2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="Q2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="R2" s="8" t="s">
         <v>15</v>
       </c>
+      <c r="S2" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
@@ -826,19 +845,25 @@
         <v>29</v>
       </c>
       <c r="M3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>26</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/server/templates/employee-template.xlsx
+++ b/server/templates/employee-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\projects\nanafruit-hrm\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E163F3F6-F101-4FC1-8E59-E57E7918C525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54EB8C1-255D-48EA-A4E2-12A884D2B819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>รหัสลายนิ้วมือ</t>
   </si>
@@ -297,6 +297,12 @@
   </si>
   <si>
     <t>OT Normal</t>
+  </si>
+  <si>
+    <t>สัญชาติ</t>
+  </si>
+  <si>
+    <t>ไทย</t>
   </si>
 </sst>
 </file>
@@ -720,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="3" customWidth="1"/>
@@ -728,27 +734,27 @@
     <col min="3" max="3" width="13.85546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" style="3" customWidth="1"/>
     <col min="5" max="5" width="25.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="20.28515625" style="3" customWidth="1"/>
-    <col min="11" max="13" width="17.28515625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="21.140625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="16.5703125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="17.85546875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="19.85546875" style="3" customWidth="1"/>
-    <col min="18" max="18" width="20.140625" style="3" customWidth="1"/>
-    <col min="19" max="19" width="19.85546875" style="3" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="3"/>
+    <col min="6" max="7" width="16.28515625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" style="3" customWidth="1"/>
+    <col min="12" max="14" width="17.28515625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" style="3" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="19.85546875" style="3" customWidth="1"/>
+    <col min="19" max="19" width="20.140625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="19.85546875" style="3" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
@@ -768,46 +774,49 @@
         <v>1</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="N2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="O2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="Q2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="R2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="S2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="T2" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
@@ -826,43 +835,46 @@
       <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="I3" s="6">
-        <v>46235</v>
       </c>
       <c r="J3" s="6">
         <v>46235</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="6">
+        <v>46235</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="T3" s="4" t="s">
         <v>34</v>
       </c>
     </row>
